--- a/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="98">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Entrée Rang de la vaccination</t>
+    <t>Rang de la vaccination</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -250,76 +250,50 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-dose-number.identifiantRangVaccination</t>
+    <t>fr-lm-dose-number.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Identifiant de l’entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-dose-number.codeRangVaccination</t>
+    <t>Identifiant de la dose de vaccin</t>
+  </si>
+  <si>
+    <t>fr-lm-dose-number.status</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Statut de la dose de vaccin</t>
+  </si>
+  <si>
+    <t>fr-lm-dose-number.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date de la dose de vaccin</t>
+  </si>
+  <si>
+    <t>fr-lm-dose-number.priority</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Code de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-dose-number.derivationRangVaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>derivation.</t>
-  </si>
-  <si>
-    <t>fr-lm-dose-number.descriptionRangVaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Partie narrative de l’entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-dose-number.statutRangVaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l’entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-dose-number.dateRangVaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de l’observation</t>
-  </si>
-  <si>
-    <t>fr-lm-dose-number.prioriteRangVaccination</t>
-  </si>
-  <si>
     <t>Priorité</t>
   </si>
   <si>
-    <t>fr-lm-dose-number.nombreRenouvellements</t>
+    <t>fr-lm-dose-number.renewal</t>
   </si>
   <si>
     <t xml:space="preserve">Range
@@ -329,20 +303,17 @@
     <t>Nombre de renouvellements possibles</t>
   </si>
   <si>
-    <t>fr-lm-dose-number.languageRangVaccination</t>
+    <t>fr-lm-dose-number.language</t>
   </si>
   <si>
     <t>Language</t>
   </si>
   <si>
-    <t>fr-lm-dose-number.rangVaccination</t>
+    <t>fr-lm-dose-number.doseNumber</t>
   </si>
   <si>
     <t xml:space="preserve">integer
 </t>
-  </si>
-  <si>
-    <t>Rang de la vaccination</t>
   </si>
 </sst>
 </file>
@@ -644,11 +615,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.10546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.10546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="26.203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.203125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -678,7 +649,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.10546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="26.203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1307,7 +1278,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>82</v>
@@ -1382,7 +1353,7 @@
         <v>91</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>82</v>
@@ -1422,13 +1393,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L8" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1496,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1507,7 +1478,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>82</v>
@@ -1522,13 +1493,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1579,10 +1550,10 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>82</v>
@@ -1591,306 +1562,6 @@
         <v>73</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
